--- a/artfynd/A 49765-2022 artfynd.xlsx
+++ b/artfynd/A 49765-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 49765-2022 artfynd.xlsx
+++ b/artfynd/A 49765-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2101,6 +2101,764 @@
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>127929652</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57663</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Västermoren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>516779</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6668806</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>färska ringhack (gran)</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Janolof Hermansson, Alec Bailey, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>127871088</v>
+      </c>
+      <c r="B14" t="n">
+        <v>90836</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5734</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Druvfingersvampar</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Ramaria botrytis s.lat.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Limnäsudden, Limnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>516732</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6668821</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Andreas Öster, Janolof Hermansson, Jonas Göransson, Alec Bailey, Patric Engfeldt, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>127929717</v>
+      </c>
+      <c r="B15" t="n">
+        <v>90836</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>5734</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Druvfingersvampar</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Ramaria botrytis s.lat.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Limnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>516738</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6668819</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>med gran</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Jonas Göransson, Andreas Öster, Janolof Hermansson, Alec Bailey, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>127929703</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98456</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Limnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>516740</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6668815</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Jonas Göransson, Andreas Öster, Janolof Hermansson, Alec Bailey, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>127929702</v>
+      </c>
+      <c r="B17" t="n">
+        <v>98456</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Limnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>516731</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6668824</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Jonas Göransson, Andreas Öster, Janolof Hermansson, Alec Bailey, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>127929661</v>
+      </c>
+      <c r="B18" t="n">
+        <v>98456</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Västermoren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>516742</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6668816</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Janolof Hermansson, Alec Bailey, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>127871178</v>
+      </c>
+      <c r="B19" t="n">
+        <v>90836</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5734</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Druvfingersvampar</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Ramaria botrytis s.lat.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Limnäsudden, Limnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>516733</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6668821</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Andreas Öster, Janolof Hermansson, Jonas Göransson, Alec Bailey, Patric Engfeldt, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 49765-2022 artfynd.xlsx
+++ b/artfynd/A 49765-2022 artfynd.xlsx
@@ -2106,7 +2106,7 @@
         <v>127929652</v>
       </c>
       <c r="B13" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>127871088</v>
       </c>
       <c r="B14" t="n">
-        <v>90836</v>
+        <v>90839</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>127929717</v>
       </c>
       <c r="B15" t="n">
-        <v>90836</v>
+        <v>90839</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>127929703</v>
       </c>
       <c r="B16" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>127929702</v>
       </c>
       <c r="B17" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
         <v>127929661</v>
       </c>
       <c r="B18" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>127871178</v>
       </c>
       <c r="B19" t="n">
-        <v>90836</v>
+        <v>90839</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 49765-2022 artfynd.xlsx
+++ b/artfynd/A 49765-2022 artfynd.xlsx
@@ -2106,7 +2106,7 @@
         <v>127929652</v>
       </c>
       <c r="B13" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>127871088</v>
       </c>
       <c r="B14" t="n">
-        <v>90839</v>
+        <v>90847</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>127929717</v>
       </c>
       <c r="B15" t="n">
-        <v>90839</v>
+        <v>90847</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>127929703</v>
       </c>
       <c r="B16" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>127929702</v>
       </c>
       <c r="B17" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
         <v>127929661</v>
       </c>
       <c r="B18" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>127871178</v>
       </c>
       <c r="B19" t="n">
-        <v>90839</v>
+        <v>90847</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 49765-2022 artfynd.xlsx
+++ b/artfynd/A 49765-2022 artfynd.xlsx
@@ -2210,10 +2210,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127871088</v>
+        <v>127929717</v>
       </c>
       <c r="B14" t="n">
-        <v>90847</v>
+        <v>90848</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2234,17 +2234,26 @@
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Limnäsudden, Limnäsudden, Dlr</t>
+          <t>Limnäsudden, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>516732</v>
+        <v>516738</v>
       </c>
       <c r="R14" t="n">
-        <v>6668821</v>
+        <v>6668819</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2274,19 +2283,14 @@
           <t>2025-08-27</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>12:02</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-27</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>12:02</t>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>med gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2301,22 +2305,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Andreas Öster, Janolof Hermansson, Jonas Göransson, Alec Bailey, Patric Engfeldt, Philipp Weiss</t>
+          <t>Patric Engfeldt, Alec Bailey, Janolof Hermansson, Andreas Öster, Jonas Göransson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127929717</v>
+        <v>127871088</v>
       </c>
       <c r="B15" t="n">
-        <v>90847</v>
+        <v>90848</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2337,26 +2341,17 @@
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Limnäsudden, Dlr</t>
+          <t>Limnäsudden, Limnäsudden, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>516738</v>
+        <v>516732</v>
       </c>
       <c r="R15" t="n">
-        <v>6668819</v>
+        <v>6668821</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2386,14 +2381,19 @@
           <t>2025-08-27</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-27</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>med gran</t>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2408,12 +2408,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Jonas Göransson, Andreas Öster, Janolof Hermansson, Alec Bailey, Patric Engfeldt</t>
+          <t>Jonas Göransson, Andreas Öster, Janolof Hermansson, Alec Bailey, Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2423,7 +2423,7 @@
         <v>127929703</v>
       </c>
       <c r="B16" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Jonas Göransson, Andreas Öster, Janolof Hermansson, Alec Bailey, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Alec Bailey, Janolof Hermansson, Andreas Öster, Jonas Göransson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2534,7 +2534,7 @@
         <v>127929702</v>
       </c>
       <c r="B17" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Jonas Göransson, Andreas Öster, Janolof Hermansson, Alec Bailey, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Alec Bailey, Janolof Hermansson, Andreas Öster, Jonas Göransson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2645,7 +2645,7 @@
         <v>127929661</v>
       </c>
       <c r="B18" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>127871178</v>
       </c>
       <c r="B19" t="n">
-        <v>90847</v>
+        <v>90848</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 49765-2022 artfynd.xlsx
+++ b/artfynd/A 49765-2022 artfynd.xlsx
@@ -2210,7 +2210,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127929717</v>
+        <v>127871088</v>
       </c>
       <c r="B14" t="n">
         <v>90848</v>
@@ -2234,26 +2234,17 @@
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Limnäsudden, Dlr</t>
+          <t>Limnäsudden, Limnäsudden, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>516738</v>
+        <v>516732</v>
       </c>
       <c r="R14" t="n">
-        <v>6668819</v>
+        <v>6668821</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2283,14 +2274,19 @@
           <t>2025-08-27</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-27</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>med gran</t>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2305,19 +2301,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Alec Bailey, Janolof Hermansson, Andreas Öster, Jonas Göransson, Philipp Weiss</t>
+          <t>Andreas Öster, Janolof Hermansson, Jonas Göransson, Alec Bailey, Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127871088</v>
+        <v>127929717</v>
       </c>
       <c r="B15" t="n">
         <v>90848</v>
@@ -2341,17 +2337,26 @@
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Limnäsudden, Limnäsudden, Dlr</t>
+          <t>Limnäsudden, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>516732</v>
+        <v>516738</v>
       </c>
       <c r="R15" t="n">
-        <v>6668821</v>
+        <v>6668819</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2381,19 +2386,14 @@
           <t>2025-08-27</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>12:02</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-27</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>12:02</t>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>med gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2408,12 +2408,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Jonas Göransson, Andreas Öster, Janolof Hermansson, Alec Bailey, Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Jonas Göransson, Andreas Öster, Janolof Hermansson, Alec Bailey, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Alec Bailey, Janolof Hermansson, Andreas Öster, Jonas Göransson, Philipp Weiss</t>
+          <t>Philipp Weiss, Jonas Göransson, Andreas Öster, Janolof Hermansson, Alec Bailey, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2635,7 +2635,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Alec Bailey, Janolof Hermansson, Andreas Öster, Jonas Göransson, Philipp Weiss</t>
+          <t>Philipp Weiss, Jonas Göransson, Andreas Öster, Janolof Hermansson, Alec Bailey, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 49765-2022 artfynd.xlsx
+++ b/artfynd/A 49765-2022 artfynd.xlsx
@@ -2213,7 +2213,7 @@
         <v>127871088</v>
       </c>
       <c r="B14" t="n">
-        <v>90848</v>
+        <v>90849</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>127929717</v>
       </c>
       <c r="B15" t="n">
-        <v>90848</v>
+        <v>90849</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>127929703</v>
       </c>
       <c r="B16" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2531,10 +2531,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127929702</v>
+        <v>127929661</v>
       </c>
       <c r="B17" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2576,14 +2576,14 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Limnäsudden, Dlr</t>
+          <t>Västermoren, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>516731</v>
+        <v>516742</v>
       </c>
       <c r="R17" t="n">
-        <v>6668824</v>
+        <v>6668816</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2618,6 +2618,11 @@
           <t>2025-08-27</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2635,17 +2640,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Jonas Göransson, Andreas Öster, Janolof Hermansson, Alec Bailey, Patric Engfeldt</t>
+          <t>Philipp Weiss, Janolof Hermansson, Alec Bailey, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127929661</v>
+        <v>127929702</v>
       </c>
       <c r="B18" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2672,7 +2677,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2687,14 +2692,14 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Västermoren, Dlr</t>
+          <t>Limnäsudden, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>516742</v>
+        <v>516731</v>
       </c>
       <c r="R18" t="n">
-        <v>6668816</v>
+        <v>6668824</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2729,11 +2734,6 @@
           <t>2025-08-27</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Alec Bailey, Patric Engfeldt</t>
+          <t>Philipp Weiss, Jonas Göransson, Andreas Öster, Janolof Hermansson, Alec Bailey, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2761,7 +2761,7 @@
         <v>127871178</v>
       </c>
       <c r="B19" t="n">
-        <v>90848</v>
+        <v>90849</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 49765-2022 artfynd.xlsx
+++ b/artfynd/A 49765-2022 artfynd.xlsx
@@ -2213,7 +2213,7 @@
         <v>127871088</v>
       </c>
       <c r="B14" t="n">
-        <v>90849</v>
+        <v>90850</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>127929717</v>
       </c>
       <c r="B15" t="n">
-        <v>90849</v>
+        <v>90850</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>127929703</v>
       </c>
       <c r="B16" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2531,10 +2531,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127929661</v>
+        <v>127929702</v>
       </c>
       <c r="B17" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2576,14 +2576,14 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Västermoren, Dlr</t>
+          <t>Limnäsudden, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>516742</v>
+        <v>516731</v>
       </c>
       <c r="R17" t="n">
-        <v>6668816</v>
+        <v>6668824</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2618,11 +2618,6 @@
           <t>2025-08-27</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2640,17 +2635,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Alec Bailey, Patric Engfeldt</t>
+          <t>Philipp Weiss, Jonas Göransson, Andreas Öster, Janolof Hermansson, Alec Bailey, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127929702</v>
+        <v>127929661</v>
       </c>
       <c r="B18" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2677,7 +2672,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2692,14 +2687,14 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Limnäsudden, Dlr</t>
+          <t>Västermoren, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>516731</v>
+        <v>516742</v>
       </c>
       <c r="R18" t="n">
-        <v>6668824</v>
+        <v>6668816</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2734,6 +2729,11 @@
           <t>2025-08-27</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Jonas Göransson, Andreas Öster, Janolof Hermansson, Alec Bailey, Patric Engfeldt</t>
+          <t>Philipp Weiss, Janolof Hermansson, Alec Bailey, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2761,7 +2761,7 @@
         <v>127871178</v>
       </c>
       <c r="B19" t="n">
-        <v>90849</v>
+        <v>90850</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 49765-2022 artfynd.xlsx
+++ b/artfynd/A 49765-2022 artfynd.xlsx
@@ -2531,7 +2531,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127929702</v>
+        <v>127929661</v>
       </c>
       <c r="B17" t="n">
         <v>98470</v>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2576,14 +2576,14 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Limnäsudden, Dlr</t>
+          <t>Västermoren, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>516731</v>
+        <v>516742</v>
       </c>
       <c r="R17" t="n">
-        <v>6668824</v>
+        <v>6668816</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2618,6 +2618,11 @@
           <t>2025-08-27</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2635,14 +2640,14 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Jonas Göransson, Andreas Öster, Janolof Hermansson, Alec Bailey, Patric Engfeldt</t>
+          <t>Philipp Weiss, Janolof Hermansson, Alec Bailey, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127929661</v>
+        <v>127929702</v>
       </c>
       <c r="B18" t="n">
         <v>98470</v>
@@ -2672,7 +2677,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2687,14 +2692,14 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Västermoren, Dlr</t>
+          <t>Limnäsudden, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>516742</v>
+        <v>516731</v>
       </c>
       <c r="R18" t="n">
-        <v>6668816</v>
+        <v>6668824</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2729,11 +2734,6 @@
           <t>2025-08-27</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Alec Bailey, Patric Engfeldt</t>
+          <t>Philipp Weiss, Jonas Göransson, Andreas Öster, Janolof Hermansson, Alec Bailey, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 49765-2022 artfynd.xlsx
+++ b/artfynd/A 49765-2022 artfynd.xlsx
@@ -2420,7 +2420,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127929703</v>
+        <v>127929661</v>
       </c>
       <c r="B16" t="n">
         <v>98470</v>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2465,14 +2465,14 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Limnäsudden, Dlr</t>
+          <t>Västermoren, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>516740</v>
+        <v>516742</v>
       </c>
       <c r="R16" t="n">
-        <v>6668815</v>
+        <v>6668816</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2507,6 +2507,11 @@
           <t>2025-08-27</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2524,14 +2529,14 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Jonas Göransson, Andreas Öster, Janolof Hermansson, Alec Bailey, Patric Engfeldt</t>
+          <t>Philipp Weiss, Janolof Hermansson, Alec Bailey, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127929661</v>
+        <v>127929702</v>
       </c>
       <c r="B17" t="n">
         <v>98470</v>
@@ -2561,7 +2566,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2576,14 +2581,14 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Västermoren, Dlr</t>
+          <t>Limnäsudden, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>516742</v>
+        <v>516731</v>
       </c>
       <c r="R17" t="n">
-        <v>6668816</v>
+        <v>6668824</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2618,11 +2623,6 @@
           <t>2025-08-27</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2640,14 +2640,14 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Alec Bailey, Patric Engfeldt</t>
+          <t>Philipp Weiss, Jonas Göransson, Andreas Öster, Janolof Hermansson, Alec Bailey, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127929702</v>
+        <v>127929703</v>
       </c>
       <c r="B18" t="n">
         <v>98470</v>
@@ -2696,10 +2696,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>516731</v>
+        <v>516740</v>
       </c>
       <c r="R18" t="n">
-        <v>6668824</v>
+        <v>6668815</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 49765-2022 artfynd.xlsx
+++ b/artfynd/A 49765-2022 artfynd.xlsx
@@ -2420,7 +2420,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127929661</v>
+        <v>127929703</v>
       </c>
       <c r="B16" t="n">
         <v>98470</v>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2465,14 +2465,14 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Västermoren, Dlr</t>
+          <t>Limnäsudden, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>516742</v>
+        <v>516740</v>
       </c>
       <c r="R16" t="n">
-        <v>6668816</v>
+        <v>6668815</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2507,11 +2507,6 @@
           <t>2025-08-27</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2529,14 +2524,14 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Alec Bailey, Patric Engfeldt</t>
+          <t>Philipp Weiss, Jonas Göransson, Andreas Öster, Janolof Hermansson, Alec Bailey, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127929702</v>
+        <v>127929661</v>
       </c>
       <c r="B17" t="n">
         <v>98470</v>
@@ -2566,7 +2561,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2581,14 +2576,14 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Limnäsudden, Dlr</t>
+          <t>Västermoren, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>516731</v>
+        <v>516742</v>
       </c>
       <c r="R17" t="n">
-        <v>6668824</v>
+        <v>6668816</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2623,6 +2618,11 @@
           <t>2025-08-27</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2640,14 +2640,14 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Jonas Göransson, Andreas Öster, Janolof Hermansson, Alec Bailey, Patric Engfeldt</t>
+          <t>Philipp Weiss, Janolof Hermansson, Alec Bailey, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127929703</v>
+        <v>127929702</v>
       </c>
       <c r="B18" t="n">
         <v>98470</v>
@@ -2696,10 +2696,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>516740</v>
+        <v>516731</v>
       </c>
       <c r="R18" t="n">
-        <v>6668815</v>
+        <v>6668824</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 49765-2022 artfynd.xlsx
+++ b/artfynd/A 49765-2022 artfynd.xlsx
@@ -2210,7 +2210,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127871088</v>
+        <v>127929717</v>
       </c>
       <c r="B14" t="n">
         <v>90850</v>
@@ -2234,17 +2234,26 @@
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Limnäsudden, Limnäsudden, Dlr</t>
+          <t>Limnäsudden, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>516732</v>
+        <v>516738</v>
       </c>
       <c r="R14" t="n">
-        <v>6668821</v>
+        <v>6668819</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2274,19 +2283,14 @@
           <t>2025-08-27</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>12:02</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-27</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>12:02</t>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>med gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2301,19 +2305,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Andreas Öster, Janolof Hermansson, Jonas Göransson, Alec Bailey, Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Jonas Göransson, Andreas Öster, Janolof Hermansson, Alec Bailey, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127929717</v>
+        <v>127871088</v>
       </c>
       <c r="B15" t="n">
         <v>90850</v>
@@ -2337,26 +2341,17 @@
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Limnäsudden, Dlr</t>
+          <t>Limnäsudden, Limnäsudden, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>516738</v>
+        <v>516732</v>
       </c>
       <c r="R15" t="n">
-        <v>6668819</v>
+        <v>6668821</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2386,14 +2381,19 @@
           <t>2025-08-27</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-27</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>med gran</t>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2408,19 +2408,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Jonas Göransson, Andreas Öster, Janolof Hermansson, Alec Bailey, Patric Engfeldt</t>
+          <t>Andreas Öster, Janolof Hermansson, Jonas Göransson, Alec Bailey, Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127929703</v>
+        <v>127929702</v>
       </c>
       <c r="B16" t="n">
         <v>98470</v>
@@ -2469,10 +2469,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>516740</v>
+        <v>516731</v>
       </c>
       <c r="R16" t="n">
-        <v>6668815</v>
+        <v>6668824</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2531,7 +2531,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127929661</v>
+        <v>127929703</v>
       </c>
       <c r="B17" t="n">
         <v>98470</v>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2576,14 +2576,14 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Västermoren, Dlr</t>
+          <t>Limnäsudden, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>516742</v>
+        <v>516740</v>
       </c>
       <c r="R17" t="n">
-        <v>6668816</v>
+        <v>6668815</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2618,11 +2618,6 @@
           <t>2025-08-27</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2640,14 +2635,14 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Alec Bailey, Patric Engfeldt</t>
+          <t>Philipp Weiss, Jonas Göransson, Andreas Öster, Janolof Hermansson, Alec Bailey, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127929702</v>
+        <v>127929661</v>
       </c>
       <c r="B18" t="n">
         <v>98470</v>
@@ -2677,7 +2672,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2692,14 +2687,14 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Limnäsudden, Dlr</t>
+          <t>Västermoren, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>516731</v>
+        <v>516742</v>
       </c>
       <c r="R18" t="n">
-        <v>6668824</v>
+        <v>6668816</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2734,6 +2729,11 @@
           <t>2025-08-27</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Jonas Göransson, Andreas Öster, Janolof Hermansson, Alec Bailey, Patric Engfeldt</t>
+          <t>Philipp Weiss, Janolof Hermansson, Alec Bailey, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 49765-2022 artfynd.xlsx
+++ b/artfynd/A 49765-2022 artfynd.xlsx
@@ -2210,7 +2210,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127929717</v>
+        <v>127871088</v>
       </c>
       <c r="B14" t="n">
         <v>90850</v>
@@ -2234,26 +2234,17 @@
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Limnäsudden, Dlr</t>
+          <t>Limnäsudden, Limnäsudden, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>516738</v>
+        <v>516732</v>
       </c>
       <c r="R14" t="n">
-        <v>6668819</v>
+        <v>6668821</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2283,14 +2274,19 @@
           <t>2025-08-27</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-27</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>med gran</t>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2305,19 +2301,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Jonas Göransson, Andreas Öster, Janolof Hermansson, Alec Bailey, Patric Engfeldt</t>
+          <t>Andreas Öster, Janolof Hermansson, Jonas Göransson, Alec Bailey, Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127871088</v>
+        <v>127929717</v>
       </c>
       <c r="B15" t="n">
         <v>90850</v>
@@ -2341,17 +2337,26 @@
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Limnäsudden, Limnäsudden, Dlr</t>
+          <t>Limnäsudden, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>516732</v>
+        <v>516738</v>
       </c>
       <c r="R15" t="n">
-        <v>6668821</v>
+        <v>6668819</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2381,19 +2386,14 @@
           <t>2025-08-27</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>12:02</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-27</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>12:02</t>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>med gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2408,19 +2408,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Andreas Öster, Janolof Hermansson, Jonas Göransson, Alec Bailey, Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Jonas Göransson, Andreas Öster, Janolof Hermansson, Alec Bailey, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127929702</v>
+        <v>127929661</v>
       </c>
       <c r="B16" t="n">
         <v>98470</v>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2465,14 +2465,14 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Limnäsudden, Dlr</t>
+          <t>Västermoren, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>516731</v>
+        <v>516742</v>
       </c>
       <c r="R16" t="n">
-        <v>6668824</v>
+        <v>6668816</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2507,6 +2507,11 @@
           <t>2025-08-27</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2524,14 +2529,14 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Jonas Göransson, Andreas Öster, Janolof Hermansson, Alec Bailey, Patric Engfeldt</t>
+          <t>Philipp Weiss, Janolof Hermansson, Alec Bailey, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127929703</v>
+        <v>127929702</v>
       </c>
       <c r="B17" t="n">
         <v>98470</v>
@@ -2580,10 +2585,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>516740</v>
+        <v>516731</v>
       </c>
       <c r="R17" t="n">
-        <v>6668815</v>
+        <v>6668824</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2642,7 +2647,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127929661</v>
+        <v>127929703</v>
       </c>
       <c r="B18" t="n">
         <v>98470</v>
@@ -2672,7 +2677,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2687,14 +2692,14 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Västermoren, Dlr</t>
+          <t>Limnäsudden, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>516742</v>
+        <v>516740</v>
       </c>
       <c r="R18" t="n">
-        <v>6668816</v>
+        <v>6668815</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2729,11 +2734,6 @@
           <t>2025-08-27</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Alec Bailey, Patric Engfeldt</t>
+          <t>Philipp Weiss, Jonas Göransson, Andreas Öster, Janolof Hermansson, Alec Bailey, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 49765-2022 artfynd.xlsx
+++ b/artfynd/A 49765-2022 artfynd.xlsx
@@ -2210,7 +2210,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127871088</v>
+        <v>127929717</v>
       </c>
       <c r="B14" t="n">
         <v>90850</v>
@@ -2234,17 +2234,26 @@
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Limnäsudden, Limnäsudden, Dlr</t>
+          <t>Limnäsudden, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>516732</v>
+        <v>516738</v>
       </c>
       <c r="R14" t="n">
-        <v>6668821</v>
+        <v>6668819</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2274,19 +2283,14 @@
           <t>2025-08-27</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>12:02</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-27</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>12:02</t>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>med gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2301,19 +2305,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Andreas Öster, Janolof Hermansson, Jonas Göransson, Alec Bailey, Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Jonas Göransson, Andreas Öster, Janolof Hermansson, Alec Bailey, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127929717</v>
+        <v>127871088</v>
       </c>
       <c r="B15" t="n">
         <v>90850</v>
@@ -2337,26 +2341,17 @@
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Limnäsudden, Dlr</t>
+          <t>Limnäsudden, Limnäsudden, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>516738</v>
+        <v>516732</v>
       </c>
       <c r="R15" t="n">
-        <v>6668819</v>
+        <v>6668821</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2386,14 +2381,19 @@
           <t>2025-08-27</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-27</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>med gran</t>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2408,12 +2408,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Jonas Göransson, Andreas Öster, Janolof Hermansson, Alec Bailey, Patric Engfeldt</t>
+          <t>Andreas Öster, Janolof Hermansson, Jonas Göransson, Alec Bailey, Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 49765-2022 artfynd.xlsx
+++ b/artfynd/A 49765-2022 artfynd.xlsx
@@ -2210,7 +2210,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127929717</v>
+        <v>127871088</v>
       </c>
       <c r="B14" t="n">
         <v>90850</v>
@@ -2234,26 +2234,17 @@
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Limnäsudden, Dlr</t>
+          <t>Limnäsudden, Limnäsudden, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>516738</v>
+        <v>516732</v>
       </c>
       <c r="R14" t="n">
-        <v>6668819</v>
+        <v>6668821</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2283,14 +2274,19 @@
           <t>2025-08-27</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-27</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>med gran</t>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2305,19 +2301,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Jonas Göransson, Andreas Öster, Janolof Hermansson, Alec Bailey, Patric Engfeldt</t>
+          <t>Andreas Öster, Janolof Hermansson, Jonas Göransson, Alec Bailey, Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127871088</v>
+        <v>127929717</v>
       </c>
       <c r="B15" t="n">
         <v>90850</v>
@@ -2341,17 +2337,26 @@
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Limnäsudden, Limnäsudden, Dlr</t>
+          <t>Limnäsudden, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>516732</v>
+        <v>516738</v>
       </c>
       <c r="R15" t="n">
-        <v>6668821</v>
+        <v>6668819</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2381,19 +2386,14 @@
           <t>2025-08-27</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>12:02</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-27</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>12:02</t>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>med gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2408,19 +2408,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Andreas Öster, Janolof Hermansson, Jonas Göransson, Alec Bailey, Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Jonas Göransson, Andreas Öster, Janolof Hermansson, Alec Bailey, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127929661</v>
+        <v>127929702</v>
       </c>
       <c r="B16" t="n">
         <v>98470</v>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2465,14 +2465,14 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Västermoren, Dlr</t>
+          <t>Limnäsudden, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>516742</v>
+        <v>516731</v>
       </c>
       <c r="R16" t="n">
-        <v>6668816</v>
+        <v>6668824</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2507,11 +2507,6 @@
           <t>2025-08-27</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2529,14 +2524,14 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Alec Bailey, Patric Engfeldt</t>
+          <t>Philipp Weiss, Jonas Göransson, Andreas Öster, Janolof Hermansson, Alec Bailey, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127929702</v>
+        <v>127929703</v>
       </c>
       <c r="B17" t="n">
         <v>98470</v>
@@ -2585,10 +2580,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>516731</v>
+        <v>516740</v>
       </c>
       <c r="R17" t="n">
-        <v>6668824</v>
+        <v>6668815</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2647,7 +2642,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127929703</v>
+        <v>127929661</v>
       </c>
       <c r="B18" t="n">
         <v>98470</v>
@@ -2677,7 +2672,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2692,14 +2687,14 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Limnäsudden, Dlr</t>
+          <t>Västermoren, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>516740</v>
+        <v>516742</v>
       </c>
       <c r="R18" t="n">
-        <v>6668815</v>
+        <v>6668816</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2734,6 +2729,11 @@
           <t>2025-08-27</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Jonas Göransson, Andreas Öster, Janolof Hermansson, Alec Bailey, Patric Engfeldt</t>
+          <t>Philipp Weiss, Janolof Hermansson, Alec Bailey, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 49765-2022 artfynd.xlsx
+++ b/artfynd/A 49765-2022 artfynd.xlsx
@@ -2106,7 +2106,7 @@
         <v>127929652</v>
       </c>
       <c r="B13" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>127871088</v>
       </c>
       <c r="B14" t="n">
-        <v>90850</v>
+        <v>90856</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>127929717</v>
       </c>
       <c r="B15" t="n">
-        <v>90850</v>
+        <v>90856</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2420,10 +2420,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127929702</v>
+        <v>127929703</v>
       </c>
       <c r="B16" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2469,10 +2469,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>516731</v>
+        <v>516740</v>
       </c>
       <c r="R16" t="n">
-        <v>6668824</v>
+        <v>6668815</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2531,10 +2531,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127929703</v>
+        <v>127929702</v>
       </c>
       <c r="B17" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2580,10 +2580,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>516740</v>
+        <v>516731</v>
       </c>
       <c r="R17" t="n">
-        <v>6668815</v>
+        <v>6668824</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2645,7 +2645,7 @@
         <v>127929661</v>
       </c>
       <c r="B18" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>127871178</v>
       </c>
       <c r="B19" t="n">
-        <v>90850</v>
+        <v>90856</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 49765-2022 artfynd.xlsx
+++ b/artfynd/A 49765-2022 artfynd.xlsx
@@ -2210,7 +2210,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127871088</v>
+        <v>127929717</v>
       </c>
       <c r="B14" t="n">
         <v>90856</v>
@@ -2234,17 +2234,26 @@
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Limnäsudden, Limnäsudden, Dlr</t>
+          <t>Limnäsudden, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>516732</v>
+        <v>516738</v>
       </c>
       <c r="R14" t="n">
-        <v>6668821</v>
+        <v>6668819</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2274,19 +2283,14 @@
           <t>2025-08-27</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>12:02</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-27</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>12:02</t>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>med gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2301,19 +2305,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Andreas Öster, Janolof Hermansson, Jonas Göransson, Alec Bailey, Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Jonas Göransson, Andreas Öster, Janolof Hermansson, Alec Bailey, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127929717</v>
+        <v>127871088</v>
       </c>
       <c r="B15" t="n">
         <v>90856</v>
@@ -2337,26 +2341,17 @@
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Limnäsudden, Dlr</t>
+          <t>Limnäsudden, Limnäsudden, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>516738</v>
+        <v>516732</v>
       </c>
       <c r="R15" t="n">
-        <v>6668819</v>
+        <v>6668821</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2386,14 +2381,19 @@
           <t>2025-08-27</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-27</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>med gran</t>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2408,12 +2408,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Jonas Göransson, Andreas Öster, Janolof Hermansson, Alec Bailey, Patric Engfeldt</t>
+          <t>Andreas Öster, Janolof Hermansson, Jonas Göransson, Alec Bailey, Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 49765-2022 artfynd.xlsx
+++ b/artfynd/A 49765-2022 artfynd.xlsx
@@ -2106,7 +2106,7 @@
         <v>127929652</v>
       </c>
       <c r="B13" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2210,10 +2210,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127929717</v>
+        <v>127871088</v>
       </c>
       <c r="B14" t="n">
-        <v>90856</v>
+        <v>90948</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2234,26 +2234,17 @@
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Limnäsudden, Dlr</t>
+          <t>Limnäsudden, Limnäsudden, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>516738</v>
+        <v>516732</v>
       </c>
       <c r="R14" t="n">
-        <v>6668819</v>
+        <v>6668821</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2283,14 +2274,19 @@
           <t>2025-08-27</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-27</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>med gran</t>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2305,22 +2301,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Jonas Göransson, Andreas Öster, Janolof Hermansson, Alec Bailey, Patric Engfeldt</t>
+          <t>Andreas Öster, Janolof Hermansson, Jonas Göransson, Alec Bailey, Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127871088</v>
+        <v>127929717</v>
       </c>
       <c r="B15" t="n">
-        <v>90856</v>
+        <v>90948</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2341,17 +2337,26 @@
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Limnäsudden, Limnäsudden, Dlr</t>
+          <t>Limnäsudden, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>516732</v>
+        <v>516738</v>
       </c>
       <c r="R15" t="n">
-        <v>6668821</v>
+        <v>6668819</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2381,19 +2386,14 @@
           <t>2025-08-27</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>12:02</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-27</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>12:02</t>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>med gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2408,12 +2408,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Andreas Öster, Janolof Hermansson, Jonas Göransson, Alec Bailey, Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Jonas Göransson, Andreas Öster, Janolof Hermansson, Alec Bailey, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2423,7 +2423,7 @@
         <v>127929703</v>
       </c>
       <c r="B16" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>127929702</v>
       </c>
       <c r="B17" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
         <v>127929661</v>
       </c>
       <c r="B18" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>127871178</v>
       </c>
       <c r="B19" t="n">
-        <v>90856</v>
+        <v>90948</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 49765-2022 artfynd.xlsx
+++ b/artfynd/A 49765-2022 artfynd.xlsx
@@ -2531,7 +2531,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127929702</v>
+        <v>127929661</v>
       </c>
       <c r="B17" t="n">
         <v>98571</v>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2576,14 +2576,14 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Limnäsudden, Dlr</t>
+          <t>Västermoren, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>516731</v>
+        <v>516742</v>
       </c>
       <c r="R17" t="n">
-        <v>6668824</v>
+        <v>6668816</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2618,6 +2618,11 @@
           <t>2025-08-27</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2635,14 +2640,14 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Jonas Göransson, Andreas Öster, Janolof Hermansson, Alec Bailey, Patric Engfeldt</t>
+          <t>Philipp Weiss, Janolof Hermansson, Alec Bailey, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127929661</v>
+        <v>127929702</v>
       </c>
       <c r="B18" t="n">
         <v>98571</v>
@@ -2672,7 +2677,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2687,14 +2692,14 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Västermoren, Dlr</t>
+          <t>Limnäsudden, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>516742</v>
+        <v>516731</v>
       </c>
       <c r="R18" t="n">
-        <v>6668816</v>
+        <v>6668824</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2729,11 +2734,6 @@
           <t>2025-08-27</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Alec Bailey, Patric Engfeldt</t>
+          <t>Philipp Weiss, Jonas Göransson, Andreas Öster, Janolof Hermansson, Alec Bailey, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 49765-2022 artfynd.xlsx
+++ b/artfynd/A 49765-2022 artfynd.xlsx
@@ -2106,7 +2106,7 @@
         <v>127929652</v>
       </c>
       <c r="B13" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2210,10 +2210,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127871088</v>
+        <v>127929717</v>
       </c>
       <c r="B14" t="n">
-        <v>90948</v>
+        <v>90960</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2234,17 +2234,26 @@
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Limnäsudden, Limnäsudden, Dlr</t>
+          <t>Limnäsudden, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>516732</v>
+        <v>516738</v>
       </c>
       <c r="R14" t="n">
-        <v>6668821</v>
+        <v>6668819</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2274,19 +2283,14 @@
           <t>2025-08-27</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>12:02</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-27</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>12:02</t>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>med gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2301,22 +2305,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Andreas Öster, Janolof Hermansson, Jonas Göransson, Alec Bailey, Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Jonas Göransson, Andreas Öster, Janolof Hermansson, Alec Bailey, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127929717</v>
+        <v>127871088</v>
       </c>
       <c r="B15" t="n">
-        <v>90948</v>
+        <v>90960</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2337,26 +2341,17 @@
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Limnäsudden, Dlr</t>
+          <t>Limnäsudden, Limnäsudden, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>516738</v>
+        <v>516732</v>
       </c>
       <c r="R15" t="n">
-        <v>6668819</v>
+        <v>6668821</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2386,14 +2381,19 @@
           <t>2025-08-27</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-27</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>med gran</t>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2408,12 +2408,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Jonas Göransson, Andreas Öster, Janolof Hermansson, Alec Bailey, Patric Engfeldt</t>
+          <t>Andreas Öster, Janolof Hermansson, Jonas Göransson, Alec Bailey, Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2423,7 +2423,7 @@
         <v>127929703</v>
       </c>
       <c r="B16" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2531,10 +2531,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127929661</v>
+        <v>127929702</v>
       </c>
       <c r="B17" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2576,14 +2576,14 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Västermoren, Dlr</t>
+          <t>Limnäsudden, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>516742</v>
+        <v>516731</v>
       </c>
       <c r="R17" t="n">
-        <v>6668816</v>
+        <v>6668824</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2618,11 +2618,6 @@
           <t>2025-08-27</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2640,17 +2635,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Alec Bailey, Patric Engfeldt</t>
+          <t>Philipp Weiss, Jonas Göransson, Andreas Öster, Janolof Hermansson, Alec Bailey, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127929702</v>
+        <v>127929661</v>
       </c>
       <c r="B18" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2677,7 +2672,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2692,14 +2687,14 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Limnäsudden, Dlr</t>
+          <t>Västermoren, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>516731</v>
+        <v>516742</v>
       </c>
       <c r="R18" t="n">
-        <v>6668824</v>
+        <v>6668816</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2734,6 +2729,11 @@
           <t>2025-08-27</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Jonas Göransson, Andreas Öster, Janolof Hermansson, Alec Bailey, Patric Engfeldt</t>
+          <t>Philipp Weiss, Janolof Hermansson, Alec Bailey, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2761,7 +2761,7 @@
         <v>127871178</v>
       </c>
       <c r="B19" t="n">
-        <v>90948</v>
+        <v>90960</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 49765-2022 artfynd.xlsx
+++ b/artfynd/A 49765-2022 artfynd.xlsx
@@ -2864,7 +2864,7 @@
         <v>129091383</v>
       </c>
       <c r="B20" t="n">
-        <v>91055</v>
+        <v>91058</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 49765-2022 artfynd.xlsx
+++ b/artfynd/A 49765-2022 artfynd.xlsx
@@ -2864,7 +2864,7 @@
         <v>129091383</v>
       </c>
       <c r="B20" t="n">
-        <v>91058</v>
+        <v>91061</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 49765-2022 artfynd.xlsx
+++ b/artfynd/A 49765-2022 artfynd.xlsx
@@ -2864,7 +2864,7 @@
         <v>129091383</v>
       </c>
       <c r="B20" t="n">
-        <v>91061</v>
+        <v>91065</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 49765-2022 artfynd.xlsx
+++ b/artfynd/A 49765-2022 artfynd.xlsx
@@ -2864,7 +2864,7 @@
         <v>129091383</v>
       </c>
       <c r="B20" t="n">
-        <v>91065</v>
+        <v>91072</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 49765-2022 artfynd.xlsx
+++ b/artfynd/A 49765-2022 artfynd.xlsx
@@ -2864,7 +2864,7 @@
         <v>129091383</v>
       </c>
       <c r="B20" t="n">
-        <v>91072</v>
+        <v>91074</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 49765-2022 artfynd.xlsx
+++ b/artfynd/A 49765-2022 artfynd.xlsx
@@ -2864,7 +2864,7 @@
         <v>129091383</v>
       </c>
       <c r="B20" t="n">
-        <v>91074</v>
+        <v>91075</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 49765-2022 artfynd.xlsx
+++ b/artfynd/A 49765-2022 artfynd.xlsx
@@ -2864,7 +2864,7 @@
         <v>129091383</v>
       </c>
       <c r="B20" t="n">
-        <v>91075</v>
+        <v>91078</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 49765-2022 artfynd.xlsx
+++ b/artfynd/A 49765-2022 artfynd.xlsx
@@ -2864,7 +2864,7 @@
         <v>129091383</v>
       </c>
       <c r="B20" t="n">
-        <v>91078</v>
+        <v>91080</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 49765-2022 artfynd.xlsx
+++ b/artfynd/A 49765-2022 artfynd.xlsx
@@ -2864,7 +2864,7 @@
         <v>129091383</v>
       </c>
       <c r="B20" t="n">
-        <v>91080</v>
+        <v>91084</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 49765-2022 artfynd.xlsx
+++ b/artfynd/A 49765-2022 artfynd.xlsx
@@ -2864,7 +2864,7 @@
         <v>129091383</v>
       </c>
       <c r="B20" t="n">
-        <v>91084</v>
+        <v>91085</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 49765-2022 artfynd.xlsx
+++ b/artfynd/A 49765-2022 artfynd.xlsx
@@ -2864,7 +2864,7 @@
         <v>129091383</v>
       </c>
       <c r="B20" t="n">
-        <v>91085</v>
+        <v>91088</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 49765-2022 artfynd.xlsx
+++ b/artfynd/A 49765-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>79826075</v>
+        <v>111778588</v>
       </c>
       <c r="B2" t="n">
-        <v>88953</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92134</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,26 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5754</v>
+        <v>1106</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -722,17 +717,17 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Flogberget, Dlr</t>
+          <t>Limnäsudden-Västermoren, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>516727.9882910247</v>
+        <v>516635</v>
       </c>
       <c r="R2" t="n">
-        <v>6668743.871237555</v>
+        <v>6668746</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,22 +751,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-09-08</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-09-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,30 +769,45 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Lågörtbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>grov hängande granlåga # Picea abies</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Pelle Adenäs</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Pelle Adenäs</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>95605430</v>
+        <v>104844570</v>
       </c>
       <c r="B3" t="n">
-        <v>88953</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -815,21 +815,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5754</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -838,17 +838,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Limnäsudden, Dlr</t>
+          <t>Limnäsudden, SV Plogen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>516732.6891078123</v>
+        <v>516711</v>
       </c>
       <c r="R3" t="n">
-        <v>6668806.625689259</v>
+        <v>6668795</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,22 +872,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-08-19</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-08-19</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-27</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>avverkningsanmält</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,69 +895,85 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>inslag av lågört</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>granlåga # Picea abies</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Andreas Öster, Maria Hindemo, Janolof Hermansson, Uno Skog, Olavi Niemelä, Helena Björnström</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>95605426</v>
+        <v>119159977</v>
       </c>
       <c r="B4" t="n">
-        <v>96367</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91435</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219874</v>
+        <v>5747</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Limnäsudden, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>516732.6891078123</v>
+        <v>516733</v>
       </c>
       <c r="R4" t="n">
-        <v>6668806.625689259</v>
+        <v>6668807</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,22 +1000,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-08-19</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-08-19</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Känd lokal. 9 fruktkroppar</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,7 +1029,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1025,44 +1040,39 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Andreas Öster, Maria Hindemo, Janolof Hermansson, Uno Skog, Olavi Niemelä, Helena Björnström</t>
+          <t>Andreas Öster, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>95729807</v>
+        <v>129091383</v>
       </c>
       <c r="B5" t="n">
-        <v>88902</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91435</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5734</v>
+        <v>5747</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Druvfingersvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramaria botrytis</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bourdot</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1079,14 +1089,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Limnäsudden, S om Plogen, Dlr</t>
+          <t>Limnäsudden, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516735.6403930836</v>
+        <v>516737</v>
       </c>
       <c r="R5" t="n">
-        <v>6668815.600927733</v>
+        <v>6668819</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1113,22 +1123,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-08-25</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-08-25</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Lika långt till en tall och gran. Tidigare artbestämd till läderdoftande fingersvamp på lukten. Luktar tydligt läder, men det finns risk att förväxla den med tallfingersvamp.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,7 +1148,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Blåbärsbarrskog</t>
+          <t>Lågörtgranskog</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1156,9 +1161,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>eller tall</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # eller tall</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1176,15 +1186,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>102962774</v>
+        <v>55044849</v>
       </c>
       <c r="B6" t="n">
-        <v>88902</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91443</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1192,45 +1197,44 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5734</v>
+        <v>5754</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Druvfingersvamp</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramaria botrytis</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bourdot</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Limnäsudden, S om viken i Plogen, Dlr</t>
+          <t>Limnäsudden vid Plogen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>516737.607908506</v>
+        <v>516725</v>
       </c>
       <c r="R6" t="n">
-        <v>6668821.584409256</v>
+        <v>6668826</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1257,22 +1261,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-09-03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-09-03</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>ca 25 ex</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1287,12 +1286,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>kalkmarksskog</t>
+          <t>Lågörtgranskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1318,63 +1312,65 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Andreas Öster, Uno Skog</t>
+          <t>Janolof Hermansson, Anders Janols</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104844570</v>
+        <v>67699383</v>
       </c>
       <c r="B7" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91443</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>5754</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Limnäsudden, SV Plogen, Dlr</t>
+          <t>Plogen S, Västermoren 475 m NV, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>516710.7963377546</v>
+        <v>516731</v>
       </c>
       <c r="R7" t="n">
-        <v>6668795.57255416</v>
+        <v>6668836</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1398,27 +1394,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-11-27</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-09-23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-11-27</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-09-23</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>avverkningsanmält</t>
+          <t>Kryptogamexkursion med SLU och Janolof Hermansson.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1433,95 +1419,76 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>inslag av lågört</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>granlåga # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Rikard Anderberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Rikard Anderberg, Maya Edlund</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>109656533</v>
+        <v>73134034</v>
       </c>
       <c r="B8" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91443</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>5754</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Västermoren - Limnäsudden, Dlr</t>
+          <t>Limnäsudden, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>516608.0008464738</v>
+        <v>516730</v>
       </c>
       <c r="R8" t="n">
-        <v>6668699.013823911</v>
+        <v>6668825</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1545,22 +1512,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-05-30</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-05-30</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1575,7 +1532,22 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Lågörtgranskog</t>
+          <t>Lågörtbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1593,66 +1565,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>111010274</v>
+        <v>79609413</v>
       </c>
       <c r="B9" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91443</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5754</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Limnäsudden vid Plogen, Dlr</t>
+          <t>Limnäsudden, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>516619.958651009</v>
+        <v>516724</v>
       </c>
       <c r="R9" t="n">
-        <v>6668701.557452653</v>
+        <v>6668832</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1679,22 +1633,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-07-23</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-08-26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-07-23</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-08-26</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1709,7 +1653,27 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Lågörtgranskog</t>
+          <t>Lågörtbarrskog</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>kalkmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1720,44 +1684,39 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Janolof Hermansson, Andreas Öster, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>111739701</v>
+        <v>79826075</v>
       </c>
       <c r="B10" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91443</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>5754</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1767,25 +1726,24 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Limnäsudden-Västermoren, Dlr</t>
+          <t>Flogberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>516720</v>
+        <v>516728</v>
       </c>
       <c r="R10" t="n">
-        <v>6668766</v>
+        <v>6668744</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1809,17 +1767,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-08-13</t>
+          <t>2019-09-08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-08-13</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Avverkningsanmäld skog</t>
+          <t>2019-09-08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1832,84 +1785,66 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Lågörtbarrskog</t>
-        </is>
-      </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Pelle Adenäs</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Pelle Adenäs</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>111778588</v>
+        <v>95605430</v>
       </c>
       <c r="B11" t="n">
-        <v>89601</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91443</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1106</v>
+        <v>5754</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Limnäsudden-Västermoren, Dlr</t>
+          <t>Limnäsudden, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>516636</v>
+        <v>516733</v>
       </c>
       <c r="R11" t="n">
-        <v>6668745</v>
+        <v>6668807</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1933,12 +1868,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
+          <t>2021-08-19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
+          <t>2021-08-19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1951,88 +1886,74 @@
       <c r="AG11" t="b">
         <v>0</v>
       </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Lågörtbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>grov hängande granlåga # Picea abies</t>
-        </is>
-      </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Andreas Öster, Maria Hindemo, Janolof Hermansson, Uno Skog, Olavi Niemelä, Helena Björnström</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119159977</v>
+        <v>111616113</v>
       </c>
       <c r="B12" t="n">
-        <v>90095</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91443</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5747</v>
+        <v>5754</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Christian</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Limnäsudden, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>516733</v>
+        <v>516726</v>
       </c>
       <c r="R12" t="n">
-        <v>6668807</v>
+        <v>6668824</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2056,27 +1977,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>13:09</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>13:09</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Känd lokal. 9 fruktkroppar</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2085,28 +1991,39 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>kalkmarksskog</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Andreas Öster, Janolof Hermansson</t>
+          <t>Janolof Hermansson, Nadja Hermansson Kovler</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127929652</v>
+        <v>127871304</v>
       </c>
       <c r="B13" t="n">
-        <v>57689</v>
+        <v>91443</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2114,39 +2031,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>5754</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Västermoren, Dlr</t>
+          <t>Limnäsudden, Limnäsudden, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>516779</v>
+        <v>516740</v>
       </c>
       <c r="R13" t="n">
-        <v>6668806</v>
+        <v>6668832</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2176,14 +2088,19 @@
           <t>2025-08-27</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-27</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>färska ringhack (gran)</t>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2198,22 +2115,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Alec Bailey, Patric Engfeldt</t>
+          <t>Andreas Öster, Janolof Hermansson, Jonas Göransson, Alec Bailey, Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127929717</v>
+        <v>127929708</v>
       </c>
       <c r="B14" t="n">
-        <v>90960</v>
+        <v>91443</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2221,22 +2138,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5734</v>
+        <v>5754</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Druvfingersvampar</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramaria botrytis s.lat.</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Ramaria testaceoflava</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2250,10 +2171,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>516738</v>
+        <v>516731</v>
       </c>
       <c r="R14" t="n">
-        <v>6668819</v>
+        <v>6668829</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2286,11 +2207,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-27</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>med gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2317,10 +2233,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127871088</v>
+        <v>16574657</v>
       </c>
       <c r="B15" t="n">
-        <v>90960</v>
+        <v>93233</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2328,33 +2244,47 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5734</v>
+        <v>5964</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Druvfingersvampar</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramaria botrytis s.lat.</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Limnäsudden, Limnäsudden, Dlr</t>
+          <t>Limnäsudden vid Plogen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>516732</v>
+        <v>516577</v>
       </c>
       <c r="R15" t="n">
-        <v>6668821</v>
+        <v>6668760</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2378,22 +2308,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>12:02</t>
+          <t>2014-09-02</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>12:02</t>
+          <t>2014-09-02</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2402,77 +2322,74 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>kalkmarksgranskog</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Andreas Öster, Janolof Hermansson, Jonas Göransson, Alec Bailey, Patric Engfeldt, Philipp Weiss</t>
+          <t>Janolof Hermansson, Ingela Källén</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127929703</v>
+        <v>127929652</v>
       </c>
       <c r="B16" t="n">
-        <v>98585</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Limnäsudden, Dlr</t>
+          <t>Västermoren, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>516740</v>
+        <v>516779</v>
       </c>
       <c r="R16" t="n">
-        <v>6668815</v>
+        <v>6668806</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2507,6 +2424,11 @@
           <t>2025-08-27</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>färska ringhack (gran)</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2524,44 +2446,44 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Jonas Göransson, Andreas Öster, Janolof Hermansson, Alec Bailey, Patric Engfeldt</t>
+          <t>Philipp Weiss, Janolof Hermansson, Alec Bailey, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127929702</v>
+        <v>16574658</v>
       </c>
       <c r="B17" t="n">
-        <v>98585</v>
+        <v>99017</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>219795</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2569,24 +2491,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Limnäsudden, Dlr</t>
+          <t>Limnäsudden vid Plogen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>516731</v>
+        <v>516577</v>
       </c>
       <c r="R17" t="n">
-        <v>6668824</v>
+        <v>6668760</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2610,12 +2529,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2014-09-02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2014-09-02</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2626,75 +2545,70 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>kalkmarksgranskog</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Jonas Göransson, Andreas Öster, Janolof Hermansson, Alec Bailey, Patric Engfeldt</t>
+          <t>Janolof Hermansson, Ingela Källén</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127929661</v>
+        <v>95605426</v>
       </c>
       <c r="B18" t="n">
-        <v>98585</v>
+        <v>99153</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Västermoren, Dlr</t>
+          <t>Limnäsudden, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>516742</v>
+        <v>516733</v>
       </c>
       <c r="R18" t="n">
-        <v>6668816</v>
+        <v>6668807</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2721,17 +2635,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2021-08-19</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
+          <t>2021-08-19</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2740,62 +2649,71 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Janolof Hermansson, Alec Bailey, Patric Engfeldt</t>
+          <t>Andreas Öster, Maria Hindemo, Janolof Hermansson, Uno Skog, Olavi Niemelä, Helena Björnström</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127871178</v>
+        <v>109656620</v>
       </c>
       <c r="B19" t="n">
-        <v>90960</v>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5734</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Druvfingersvampar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ramaria botrytis s.lat.</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Limnäsudden, Limnäsudden, Dlr</t>
+          <t>Västermoren - Limnäsudden, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>516733</v>
+        <v>516474</v>
       </c>
       <c r="R19" t="n">
-        <v>6668821</v>
+        <v>6668595</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2819,22 +2737,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>12:02</t>
+          <t>2023-05-30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>12:02</t>
+          <t>2023-05-30</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>ca 50 plantor på 2x2 meter</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2843,28 +2756,34 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Andreas Öster, Janolof Hermansson, Jonas Göransson, Alec Bailey, Patric Engfeldt, Philipp Weiss</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129091383</v>
+        <v>111010274</v>
       </c>
       <c r="B20" t="n">
-        <v>91088</v>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2872,45 +2791,50 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5747</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Limnäsudden, Dlr</t>
+          <t>Limnäsudden vid Plogen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>516737</v>
+        <v>516620</v>
       </c>
       <c r="R20" t="n">
-        <v>6668819</v>
+        <v>6668701</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2937,17 +2861,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2023-07-23</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Lika långt till en tall och gran. Tidigare artbestämd till läderdoftande fingersvamp på lukten. Luktar tydligt läder, men det finns risk att förväxla den med tallfingersvamp.</t>
+          <t>2023-07-23</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2965,26 +2884,6 @@
           <t>Lågörtgranskog</t>
         </is>
       </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL20" t="inlineStr">
-        <is>
-          <t>eller tall</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Picea abies # eller tall</t>
-        </is>
-      </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
@@ -2997,6 +2896,918 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>111631405</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Plogens södra ände, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>516738</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6668839</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2023-08-22</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2023-08-22</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>111739701</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Limnäsudden-Västermoren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>516720</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6668765</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2023-08-13</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2023-08-13</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Avverkningsanmäld skog</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Lågörtbarrskog</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>127929661</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Västermoren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>516742</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6668816</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Janolof Hermansson, Alec Bailey, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>127929702</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Limnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>516731</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6668824</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Jonas Göransson, Andreas Öster, Janolof Hermansson, Alec Bailey, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>127929703</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Limnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>516740</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6668815</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Jonas Göransson, Andreas Öster, Janolof Hermansson, Alec Bailey, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>16574659</v>
+      </c>
+      <c r="B26" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Limnäsudden vid Plogen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>516577</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6668760</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2014-09-02</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2014-09-02</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>kalkmarksgranskog</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson, Ingela Källén</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>109656533</v>
+      </c>
+      <c r="B27" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Västermoren - Limnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>516608</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6668699</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2023-05-30</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2023-05-30</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>111777288</v>
+      </c>
+      <c r="B28" t="n">
+        <v>91420</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>256335</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Taggfingersvamp</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Ramaria karstenii</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Sacc. &amp; P.Syd.) Corner</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Limnäsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>516731</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6668825</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2023-08-29</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2023-08-29</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>kalkmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson, Martin Gotink</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49765-2022 artfynd.xlsx
+++ b/artfynd/A 49765-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AZ28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -801,6 +806,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111778588</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -932,6 +942,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104844570</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1044,6 +1059,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119159977</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1183,6 +1203,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129091383</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1316,6 +1341,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55044849</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1434,6 +1464,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67699383</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1562,6 +1597,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73134034</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1688,6 +1728,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79609413</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1797,6 +1842,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79826075</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1898,6 +1948,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95605430</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2017,6 +2072,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111616113</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2124,6 +2184,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127871304</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2230,6 +2295,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127929708</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2343,6 +2413,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16574657</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2450,6 +2525,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127929652</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2563,6 +2643,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16574658</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2665,6 +2750,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95605426</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2777,6 +2867,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109656620</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2896,6 +2991,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111010274</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3004,6 +3104,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111631405</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3124,6 +3229,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111739701</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3240,6 +3350,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127929661</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3351,6 +3466,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127929702</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3462,6 +3582,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127929703</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3567,6 +3692,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16574659</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3674,6 +3804,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109656533</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3808,8 +3943,42 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111777288</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>